--- a/reports/over_billed.xlsx
+++ b/reports/over_billed.xlsx
@@ -14207,13 +14207,13 @@
         <v>1</v>
       </c>
       <c r="AN64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ64">
         <v>1</v>
@@ -14228,7 +14228,7 @@
         <v>1228</v>
       </c>
       <c r="AU64" t="s">
-        <v>1228</v>
+        <v>1286</v>
       </c>
       <c r="AV64" t="s">
         <v>728</v>
@@ -14362,13 +14362,13 @@
         <v>1</v>
       </c>
       <c r="AN65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ65">
         <v>2</v>
@@ -14383,7 +14383,7 @@
         <v>1228</v>
       </c>
       <c r="AU65" t="s">
-        <v>1286</v>
+        <v>1228</v>
       </c>
       <c r="AV65" t="s">
         <v>1227</v>
@@ -15682,7 +15682,7 @@
         <v>420</v>
       </c>
       <c r="O74" s="2">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="P74" t="s">
         <v>504</v>
@@ -15837,7 +15837,7 @@
         <v>420</v>
       </c>
       <c r="O75" s="2">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="P75" t="s">
         <v>504</v>
